--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스 터미널점</t>
+          <t>정글짐 구남점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mindfitness5@naver.com</t>
+          <t>junglegyminherfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1302-0795</t>
+          <t>0507-1380-2950</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>제주 제주시 서광로 167 3층 마인드휘트니스</t>
+          <t>제주 제주시 구남동8길 58 올레마트 2층 정글짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness5</t>
+          <t>https://blog.naver.com/junglegyminherfit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs1gf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>866</v>
+        <v>126</v>
       </c>
       <c r="Q2" t="n">
-        <v>643</v>
+        <v>83</v>
       </c>
       <c r="R2" t="n">
-        <v>1509</v>
+        <v>209</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1161375366</t>
+          <t>1471742099</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161375366</t>
+          <t>https://m.place.naver.com/place/1471742099</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>정글짐 구남점</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>junglegyminherfit@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1380-2950</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 구남동8길 58 올레마트 2층 정글짐</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/junglegyminherfit</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>126</v>
+        <v>1536</v>
       </c>
       <c r="Q3" t="n">
-        <v>83</v>
+        <v>541</v>
       </c>
       <c r="R3" t="n">
-        <v>209</v>
+        <v>2077</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1471742099</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471742099</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>mindfitness7@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1352-0797</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://blog.naver.com/mindfitness7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/w4yf5p</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1536</v>
+        <v>741</v>
       </c>
       <c r="Q4" t="n">
-        <v>541</v>
+        <v>768</v>
       </c>
       <c r="R4" t="n">
-        <v>2077</v>
+        <v>1509</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1069617460</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1069617460</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -918,10 +918,10 @@
         <v>321</v>
       </c>
       <c r="Q5" t="n">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="R5" t="n">
-        <v>1672</v>
+        <v>1679</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>리빌드짐 제주점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>redgym-jeju@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1497-3704</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/rebuildgym_jeju/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/wn4syol</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2147</v>
+        <v>1764</v>
       </c>
       <c r="Q6" t="n">
-        <v>507</v>
+        <v>92</v>
       </c>
       <c r="R6" t="n">
-        <v>2654</v>
+        <v>1856</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1406686676</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1406686676</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리빌드짐 제주점</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>redgym-jeju@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1497-3704</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rebuildgym_jeju/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4syol</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1764</v>
+        <v>2149</v>
       </c>
       <c r="Q7" t="n">
-        <v>92</v>
+        <v>507</v>
       </c>
       <c r="R7" t="n">
-        <v>1856</v>
+        <v>2656</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1406686676</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406686676</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1212,10 +1212,10 @@
         <v>1819</v>
       </c>
       <c r="Q8" t="n">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="R8" t="n">
-        <v>2880</v>
+        <v>2887</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>F45 제주</t>
+          <t>바름휘트니스 노형점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jh4332@naver.com</t>
+          <t>bareum_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1388-4889</t>
+          <t>0507-1302-4841</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 377 2층</t>
+          <t>제주 제주시 원노형로 54 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_jeju_</t>
+          <t>https://blog.naver.com/bareum_fitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xp35</t>
+          <t>https://talk.naver.com/ct/wfn65t0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>72</v>
+        <v>395</v>
       </c>
       <c r="Q9" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="R9" t="n">
-        <v>128</v>
+        <v>480</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1238964473</t>
+          <t>1318401535</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1238964473</t>
+          <t>https://m.place.naver.com/place/1318401535</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1344,25 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>원핏 시청점</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>onegdrgolfacademy@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1439-0799</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 광양10길 10 4층</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onefit_cityhall?igsh=dGM0ejgzNnN6czI3</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wrop</t>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>402</v>
+        <v>819</v>
       </c>
       <c r="Q10" t="n">
-        <v>45</v>
+        <v>780</v>
       </c>
       <c r="R10" t="n">
-        <v>447</v>
+        <v>1599</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1517075976</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517075976</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1438,93 +1442,187 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 이도점</t>
+          <t>원핏 시청점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humake_ido@naver.com</t>
+          <t>onegdrgolfacademy@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1355-2179</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>제주 제주시 광양10길 10 4층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onefit_cityhall?igsh=dGM0ejgzNnN6czI3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wrop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>405</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>45</v>
+      </c>
+      <c r="R11" t="n">
+        <v>450</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1517075976</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1517075976</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>휴메이크휘트니스 이도점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>humake_ido@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1355-2179</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/humake_ido</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/whys2qr</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>616</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>144</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>760</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>965909506</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/965909506</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마인드휘트니스 PT&amp;필라테스&amp;요가 동홍점</t>
+          <t>맥시멈 스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mindfitness7@naver.com</t>
+          <t>maximum_jeju@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1352-0797</t>
+          <t>0507-1313-9534</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 2층,3층</t>
+          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness7</t>
+          <t>https://blog.naver.com/maximum_jeju</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4yf5p</t>
+          <t>https://talk.naver.com/ct/wha4q04</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>741</v>
+        <v>321</v>
       </c>
       <c r="Q4" t="n">
-        <v>768</v>
+        <v>1363</v>
       </c>
       <c r="R4" t="n">
-        <v>1509</v>
+        <v>1684</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1069617460</t>
+          <t>1899196588</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069617460</t>
+          <t>https://m.place.naver.com/place/1899196588</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>맥시멈 스포츠&amp;웰니스</t>
+          <t>리빌드짐 제주점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>maximum_jeju@naver.com</t>
+          <t>redgym-jeju@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1313-9534</t>
+          <t>0507-1497-3704</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
+          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/maximum_jeju</t>
+          <t>https://www.instagram.com/rebuildgym_jeju/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wha4q04</t>
+          <t>https://talk.naver.com/ct/wn4syol</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>321</v>
+        <v>1764</v>
       </c>
       <c r="Q5" t="n">
-        <v>1358</v>
+        <v>92</v>
       </c>
       <c r="R5" t="n">
-        <v>1679</v>
+        <v>1856</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1899196588</t>
+          <t>1406686676</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899196588</t>
+          <t>https://m.place.naver.com/place/1406686676</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리빌드짐 제주점</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>redgym-jeju@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1497-3704</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rebuildgym_jeju/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4syol</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1764</v>
+        <v>2149</v>
       </c>
       <c r="Q6" t="n">
-        <v>92</v>
+        <v>507</v>
       </c>
       <c r="R6" t="n">
-        <v>1856</v>
+        <v>2656</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1406686676</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406686676</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>유휘트니스 센트럴점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>ecodnc_jeju@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1338-7221</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 신대로 104 2층 유휘트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://blog.naver.com/ecodnc_jeju</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/w44oiy</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2149</v>
+        <v>1819</v>
       </c>
       <c r="Q7" t="n">
-        <v>507</v>
+        <v>1068</v>
       </c>
       <c r="R7" t="n">
-        <v>2656</v>
+        <v>2887</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1478286020</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1478286020</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>유휘트니스 센트럴점</t>
+          <t>바름휘트니스 노형점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ecodnc_jeju@naver.com</t>
+          <t>bareum_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1338-7221</t>
+          <t>0507-1302-4841</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 신대로 104 2층 유휘트니스</t>
+          <t>제주 제주시 원노형로 54 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ecodnc_jeju</t>
+          <t>https://blog.naver.com/bareum_fitness</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44oiy</t>
+          <t>https://talk.naver.com/ct/wfn65t0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1819</v>
+        <v>395</v>
       </c>
       <c r="Q8" t="n">
-        <v>1068</v>
+        <v>85</v>
       </c>
       <c r="R8" t="n">
-        <v>2887</v>
+        <v>480</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1478286020</t>
+          <t>1318401535</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478286020</t>
+          <t>https://m.place.naver.com/place/1318401535</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바름휘트니스 노형점</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bareum_fitness@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1302-4841</t>
+          <t>0507-1439-0799</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 원노형로 54 3층</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bareum_fitness</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfn65t0</t>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>395</v>
+        <v>819</v>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>780</v>
       </c>
       <c r="R9" t="n">
-        <v>480</v>
+        <v>1599</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1318401535</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1318401535</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,29 +1344,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>원핏 시청점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>onegdrgolfacademy@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1439-0799</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 제주시 광양10길 10 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://www.instagram.com/onefit_cityhall?igsh=dGM0ejgzNnN6czI3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/w5wrop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>819</v>
+        <v>405</v>
       </c>
       <c r="Q10" t="n">
-        <v>780</v>
+        <v>45</v>
       </c>
       <c r="R10" t="n">
-        <v>1599</v>
+        <v>450</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>1517075976</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/1517075976</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,25 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>원핏 시청점</t>
+          <t>휴메이크휘트니스 이도점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>onegdrgolfacademy@naver.com</t>
+          <t>humake_ido@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1355-2179</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 광양10길 10 4층</t>
+          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onefit_cityhall?igsh=dGM0ejgzNnN6czI3</t>
+          <t>https://blog.naver.com/humake_ido</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wrop</t>
+          <t>https://talk.naver.com/ct/whys2qr</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>405</v>
+        <v>616</v>
       </c>
       <c r="Q11" t="n">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="R11" t="n">
-        <v>450</v>
+        <v>760</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1517075976</t>
+          <t>965909506</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517075976</t>
+          <t>https://m.place.naver.com/place/965909506</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1531,34 +1531,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 이도점</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>humake_ido@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1355-2179</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humake_ido</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whys2qr</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>616</v>
+        <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="R12" t="n">
-        <v>760</v>
+        <v>317</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>965909506</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/965909506</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>유휘트니스 센트럴점</t>
+          <t>F45 제주</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ecodnc_jeju@naver.com</t>
+          <t>jh4332@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1338-7221</t>
+          <t>0507-1388-4889</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 신대로 104 2층 유휘트니스</t>
+          <t>제주 제주시 중앙로 377 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ecodnc_jeju</t>
+          <t>https://www.instagram.com/f45_jeju_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44oiy</t>
+          <t>https://talk.naver.com/ct/w5xp35</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1819</v>
+        <v>73</v>
       </c>
       <c r="Q7" t="n">
-        <v>1068</v>
+        <v>56</v>
       </c>
       <c r="R7" t="n">
-        <v>2887</v>
+        <v>129</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1478286020</t>
+          <t>1238964473</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478286020</t>
+          <t>https://m.place.naver.com/place/1238964473</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바름휘트니스 노형점</t>
+          <t>유휘트니스 센트럴점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bareum_fitness@naver.com</t>
+          <t>ecodnc_jeju@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1302-4841</t>
+          <t>0507-1338-7221</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 원노형로 54 3층</t>
+          <t>제주 제주시 신대로 104 2층 유휘트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bareum_fitness</t>
+          <t>https://blog.naver.com/ecodnc_jeju</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfn65t0</t>
+          <t>https://talk.naver.com/ct/w44oiy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>395</v>
+        <v>1819</v>
       </c>
       <c r="Q8" t="n">
-        <v>85</v>
+        <v>1071</v>
       </c>
       <c r="R8" t="n">
-        <v>480</v>
+        <v>2890</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1318401535</t>
+          <t>1478286020</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1318401535</t>
+          <t>https://m.place.naver.com/place/1478286020</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1246,29 +1246,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>원핏 시청점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>onegdrgolfacademy@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1439-0799</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 제주시 광양10길 10 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://www.instagram.com/onefit_cityhall?igsh=dGM0ejgzNnN6czI3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/w5wrop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>819</v>
+        <v>405</v>
       </c>
       <c r="Q9" t="n">
-        <v>780</v>
+        <v>45</v>
       </c>
       <c r="R9" t="n">
-        <v>1599</v>
+        <v>450</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>1517075976</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/1517075976</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,25 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>원핏 시청점</t>
+          <t>휴메이크휘트니스 이도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>onegdrgolfacademy@naver.com</t>
+          <t>humake_ido@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1355-2179</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 광양10길 10 4층</t>
+          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onefit_cityhall?igsh=dGM0ejgzNnN6czI3</t>
+          <t>https://blog.naver.com/humake_ido</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wrop</t>
+          <t>https://talk.naver.com/ct/whys2qr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>405</v>
+        <v>616</v>
       </c>
       <c r="Q10" t="n">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="R10" t="n">
-        <v>450</v>
+        <v>760</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1517075976</t>
+          <t>965909506</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517075976</t>
+          <t>https://m.place.naver.com/place/965909506</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1438,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 이도점</t>
+          <t>유제이 PT&amp;필라테스 노형점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humake_ido@naver.com</t>
+          <t>ohssang988@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1355-2179</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
+          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humake_ido</t>
+          <t>https://www.instagram.com/uj_pt0125</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whys2qr</t>
+          <t>https://talk.naver.com/ct/wn4n9ww</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>616</v>
+        <v>176</v>
       </c>
       <c r="Q11" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R11" t="n">
-        <v>760</v>
+        <v>316</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>965909506</t>
+          <t>1722027239</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/965909506</t>
+          <t>https://m.place.naver.com/place/1722027239</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>맥시멈 스포츠&amp;웰니스</t>
+          <t>플랜티휘트니스 노형점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>maximum_jeju@naver.com</t>
+          <t>plant4_nohyoung@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1313-9534</t>
+          <t>0507-1396-6261</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
+          <t>제주 제주시 도령로 11 6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/maximum_jeju</t>
+          <t>https://www.instagram.com/plan.t_4?igsh=MXIyOTZxbTRsdWlqaA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wha4q04</t>
+          <t>https://talk.naver.com/ct/wi1dn9g</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>321</v>
+        <v>225</v>
       </c>
       <c r="Q4" t="n">
-        <v>1363</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1684</v>
+        <v>227</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1899196588</t>
+          <t>2056218140</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899196588</t>
+          <t>https://m.place.naver.com/place/2056218140</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리빌드짐 제주점</t>
+          <t>맥시멈 스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>redgym-jeju@naver.com</t>
+          <t>maximum_jeju@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1497-3704</t>
+          <t>0507-1313-9534</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
+          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rebuildgym_jeju/</t>
+          <t>https://blog.naver.com/maximum_jeju</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4syol</t>
+          <t>https://talk.naver.com/ct/wha4q04</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1764</v>
+        <v>321</v>
       </c>
       <c r="Q5" t="n">
-        <v>92</v>
+        <v>1367</v>
       </c>
       <c r="R5" t="n">
-        <v>1856</v>
+        <v>1688</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1406686676</t>
+          <t>1899196588</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406686676</t>
+          <t>https://m.place.naver.com/place/1899196588</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>리빌드짐 제주점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>redgym-jeju@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1497-3704</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/rebuildgym_jeju/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/wn4syol</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2149</v>
+        <v>1764</v>
       </c>
       <c r="Q6" t="n">
-        <v>507</v>
+        <v>92</v>
       </c>
       <c r="R6" t="n">
-        <v>2656</v>
+        <v>1856</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1406686676</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1406686676</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F45 제주</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jh4332@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1388-4889</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 377 2층</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_jeju_</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xp35</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>73</v>
+        <v>2149</v>
       </c>
       <c r="Q7" t="n">
-        <v>56</v>
+        <v>507</v>
       </c>
       <c r="R7" t="n">
-        <v>129</v>
+        <v>2656</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1238964473</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1238964473</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>유휘트니스 센트럴점</t>
+          <t>F45 제주</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ecodnc_jeju@naver.com</t>
+          <t>jh4332@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1338-7221</t>
+          <t>0507-1388-4889</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 신대로 104 2층 유휘트니스</t>
+          <t>제주 제주시 중앙로 377 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ecodnc_jeju</t>
+          <t>https://www.instagram.com/f45_jeju_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44oiy</t>
+          <t>https://talk.naver.com/ct/w5xp35</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1819</v>
+        <v>73</v>
       </c>
       <c r="Q8" t="n">
-        <v>1071</v>
+        <v>56</v>
       </c>
       <c r="R8" t="n">
-        <v>2890</v>
+        <v>129</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1478286020</t>
+          <t>1238964473</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478286020</t>
+          <t>https://m.place.naver.com/place/1238964473</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1246,25 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>원핏 시청점</t>
+          <t>유휘트니스 센트럴점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>onegdrgolfacademy@naver.com</t>
+          <t>ecodnc_jeju@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1338-7221</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 광양10길 10 4층</t>
+          <t>제주 제주시 신대로 104 2층 유휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onefit_cityhall?igsh=dGM0ejgzNnN6czI3</t>
+          <t>https://blog.naver.com/ecodnc_jeju</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wrop</t>
+          <t>https://talk.naver.com/ct/w44oiy</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>405</v>
+        <v>1819</v>
       </c>
       <c r="Q9" t="n">
-        <v>45</v>
+        <v>1071</v>
       </c>
       <c r="R9" t="n">
-        <v>450</v>
+        <v>2890</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1517075976</t>
+          <t>1478286020</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517075976</t>
+          <t>https://m.place.naver.com/place/1478286020</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 이도점</t>
+          <t>헬플랙스 삼화점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humake_ido@naver.com</t>
+          <t>healthflex@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1355-2179</t>
+          <t>0507-1329-6759</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
+          <t>제주 제주시 동화로 56 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humake_ido</t>
+          <t>https://www.instagram.com/healthflex_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whys2qr</t>
+          <t>https://talk.naver.com/ct/w5yowk</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>616</v>
+        <v>573</v>
       </c>
       <c r="Q10" t="n">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="R10" t="n">
-        <v>760</v>
+        <v>687</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>965909506</t>
+          <t>1983341989</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/965909506</t>
+          <t>https://m.place.naver.com/place/1983341989</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유제이 PT&amp;필라테스 노형점</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ohssang988@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1439-0799</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uj_pt0125</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4n9ww</t>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>176</v>
+        <v>819</v>
       </c>
       <c r="Q11" t="n">
-        <v>140</v>
+        <v>780</v>
       </c>
       <c r="R11" t="n">
-        <v>316</v>
+        <v>1599</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,115 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1722027239</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722027239</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>atlascs@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1341-0145</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>제주 제주시 과천로 31 4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>129</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>188</v>
-      </c>
-      <c r="R12" t="n">
-        <v>317</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>37264400</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37264400</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -624,10 +624,10 @@
         <v>126</v>
       </c>
       <c r="Q2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>321</v>
       </c>
       <c r="Q5" t="n">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="R5" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1344,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헬플랙스 삼화점</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>healthflex@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1329-6759</t>
+          <t>0507-1439-0799</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 동화로 56 2층</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthflex_official</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yowk</t>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>573</v>
+        <v>819</v>
       </c>
       <c r="Q10" t="n">
-        <v>114</v>
+        <v>780</v>
       </c>
       <c r="R10" t="n">
-        <v>687</v>
+        <v>1599</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1983341989</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983341989</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>휴메이크휘트니스 이도점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>humake_ido@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1439-0799</t>
+          <t>0507-1355-2179</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://blog.naver.com/humake_ido</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/whys2qr</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>819</v>
+        <v>616</v>
       </c>
       <c r="Q11" t="n">
-        <v>780</v>
+        <v>144</v>
       </c>
       <c r="R11" t="n">
-        <v>1599</v>
+        <v>760</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,15 +1518,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>965909506</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/965909506</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>아틀라스&amp;바른자세 운동센터</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>atlascs@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1341-0145</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>제주 제주시 과천로 31 4층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jejuatlas/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>188</v>
+      </c>
+      <c r="R12" t="n">
+        <v>317</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>37264400</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37264400</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>플랜티휘트니스 노형점</t>
+          <t>사람휘트니스 이도7호점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>plant4_nohyoung@naver.com</t>
+          <t>saram_ido@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1396-6261</t>
+          <t>0507-1404-1264</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 11 6층</t>
+          <t>제주 제주시 연삼로 424</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/plan.t_4?igsh=MXIyOTZxbTRsdWlqaA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/saram_ido</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi1dn9g</t>
+          <t>https://talk.naver.com/ct/w5yc0j</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>225</v>
+        <v>273</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>461</v>
       </c>
       <c r="R4" t="n">
-        <v>227</v>
+        <v>734</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2056218140</t>
+          <t>1089331988</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056218140</t>
+          <t>https://m.place.naver.com/place/1089331988</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="Q7" t="n">
         <v>507</v>
       </c>
       <c r="R7" t="n">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유휘트니스 센트럴점</t>
+          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ecodnc_jeju@naver.com</t>
+          <t>mindfitness15@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1338-7221</t>
+          <t>0507-1439-0799</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 신대로 104 2층 유휘트니스</t>
+          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ecodnc_jeju</t>
+          <t>https://blog.naver.com/mindfitness15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44oiy</t>
+          <t>https://talk.naver.com/ct/w4g2g5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1819</v>
+        <v>819</v>
       </c>
       <c r="Q9" t="n">
-        <v>1071</v>
+        <v>781</v>
       </c>
       <c r="R9" t="n">
-        <v>2890</v>
+        <v>1600</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1478286020</t>
+          <t>1485921447</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478286020</t>
+          <t>https://m.place.naver.com/place/1485921447</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>휴메이크휘트니스 이도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>humake_ido@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1439-0799</t>
+          <t>0507-1355-2179</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://blog.naver.com/humake_ido</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
+          <t>https://talk.naver.com/ct/whys2qr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>819</v>
+        <v>617</v>
       </c>
       <c r="Q10" t="n">
-        <v>780</v>
+        <v>145</v>
       </c>
       <c r="R10" t="n">
-        <v>1599</v>
+        <v>762</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>965909506</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/965909506</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 이도점</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humake_ido@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1355-2179</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humake_ido</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whys2qr</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>616</v>
+        <v>129</v>
       </c>
       <c r="Q11" t="n">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="R11" t="n">
-        <v>760</v>
+        <v>317</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,113 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>965909506</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/965909506</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>atlascs@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1341-0145</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>제주 제주시 과천로 31 4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>129</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>188</v>
-      </c>
-      <c r="R12" t="n">
-        <v>317</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>37264400</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37264400</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="Q3" t="n">
         <v>541</v>
       </c>
       <c r="R3" t="n">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>사람휘트니스 이도7호점</t>
+          <t>맥시멈 스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>saram_ido@naver.com</t>
+          <t>maximum_jeju@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1404-1264</t>
+          <t>0507-1313-9534</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 424</t>
+          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/saram_ido</t>
+          <t>https://blog.naver.com/maximum_jeju</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yc0j</t>
+          <t>https://talk.naver.com/ct/wha4q04</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="Q4" t="n">
-        <v>461</v>
+        <v>1368</v>
       </c>
       <c r="R4" t="n">
-        <v>734</v>
+        <v>1689</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1089331988</t>
+          <t>1899196588</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089331988</t>
+          <t>https://m.place.naver.com/place/1899196588</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>맥시멈 스포츠&amp;웰니스</t>
+          <t>리빌드짐 제주점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>maximum_jeju@naver.com</t>
+          <t>redgym-jeju@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1313-9534</t>
+          <t>0507-1497-3704</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
+          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/maximum_jeju</t>
+          <t>https://www.instagram.com/rebuildgym_jeju/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wha4q04</t>
+          <t>https://talk.naver.com/ct/wn4syol</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>321</v>
+        <v>1764</v>
       </c>
       <c r="Q5" t="n">
-        <v>1368</v>
+        <v>92</v>
       </c>
       <c r="R5" t="n">
-        <v>1689</v>
+        <v>1856</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1899196588</t>
+          <t>1406686676</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899196588</t>
+          <t>https://m.place.naver.com/place/1406686676</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리빌드짐 제주점</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>redgym-jeju@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1497-3704</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rebuildgym_jeju/</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4syol</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1764</v>
+        <v>2151</v>
       </c>
       <c r="Q6" t="n">
-        <v>92</v>
+        <v>507</v>
       </c>
       <c r="R6" t="n">
-        <v>1856</v>
+        <v>2658</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1406686676</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406686676</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>F45 제주</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>jh4332@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1388-4889</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 중앙로 377 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/f45_jeju_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/w5xp35</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2150</v>
+        <v>73</v>
       </c>
       <c r="Q7" t="n">
-        <v>507</v>
+        <v>56</v>
       </c>
       <c r="R7" t="n">
-        <v>2657</v>
+        <v>129</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1238964473</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1238964473</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F45 제주</t>
+          <t>유제이 PT&amp;필라테스 노형점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jh4332@naver.com</t>
+          <t>ohssang988@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1388-4889</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 377 2층</t>
+          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_jeju_</t>
+          <t>https://www.instagram.com/uj_pt0125</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xp35</t>
+          <t>https://talk.naver.com/ct/wn4n9ww</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="R8" t="n">
-        <v>129</v>
+        <v>316</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1238964473</t>
+          <t>1722027239</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1238964473</t>
+          <t>https://m.place.naver.com/place/1722027239</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 노형점 헬스&amp;PT&amp;필라테스</t>
+          <t>트리플짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness15@naver.com</t>
+          <t>jejutriplegym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1439-0799</t>
+          <t>0507-1309-9085</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 월랑로 1 8층, 9층 마인드휘트니스 노형점</t>
+          <t>제주 제주시 동문로16길 5 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness15</t>
+          <t>https://blog.naver.com/jejutriplegym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1288,14 +1284,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4g2g5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>819</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>781</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1600</v>
+        <v>5</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1314,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485921447</t>
+          <t>2028777149</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485921447</t>
+          <t>https://m.place.naver.com/place/2028777149</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 이도점</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humake_ido@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1355-2179</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humake_ido</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whys2qr</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>617</v>
+        <v>129</v>
       </c>
       <c r="Q10" t="n">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="R10" t="n">
-        <v>762</v>
+        <v>317</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1412,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>965909506</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/965909506</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>트레이닝 스타</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>trainingstar@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1341-0145</t>
+          <t>0507-1325-9817</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주 제주시 노형로 353 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>https://blog.naver.com/trainingstar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
+          <t>https://talk.naver.com/ct/w4dvi3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="Q11" t="n">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>317</v>
+        <v>71</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>1875737855</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/1875737855</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>정글짐 구남점</t>
+          <t>사람휘트니스 이도7호점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>junglegyminherfit@naver.com</t>
+          <t>saram_ido@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1380-2950</t>
+          <t>0507-1404-1264</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>제주 제주시 구남동8길 58 올레마트 2층 정글짐</t>
+          <t>제주 제주시 연삼로 424</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/junglegyminherfit</t>
+          <t>https://blog.naver.com/saram_ido</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yc0j</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -617,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="Q2" t="n">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="R2" t="n">
-        <v>210</v>
+        <v>734</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1471742099</t>
+          <t>1089331988</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471742099</t>
+          <t>https://m.place.naver.com/place/1089331988</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>맥시멈 스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>maximum_jeju@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1468-2371</t>
+          <t>0507-1313-9534</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://blog.naver.com/maximum_jeju</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/wha4q04</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1538</v>
+        <v>321</v>
       </c>
       <c r="Q3" t="n">
-        <v>541</v>
+        <v>1374</v>
       </c>
       <c r="R3" t="n">
-        <v>2079</v>
+        <v>1695</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1899196588</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1899196588</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>맥시멈 스포츠&amp;웰니스</t>
+          <t>유휘트니스 센트럴점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>maximum_jeju@naver.com</t>
+          <t>ecodnc_jeju@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1313-9534</t>
+          <t>0507-1338-7221</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
+          <t>제주 제주시 신대로 104 2층 유휘트니��</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/maximum_jeju</t>
+          <t>https://blog.naver.com/ecodnc_jeju</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wha4q04</t>
+          <t>https://talk.naver.com/ct/w44oiy</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>321</v>
+        <v>1825</v>
       </c>
       <c r="Q4" t="n">
-        <v>1368</v>
+        <v>1074</v>
       </c>
       <c r="R4" t="n">
-        <v>1689</v>
+        <v>2899</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1899196588</t>
+          <t>1478286020</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899196588</t>
+          <t>https://m.place.naver.com/place/1478286020</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="Q6" t="n">
         <v>507</v>
       </c>
       <c r="R6" t="n">
-        <v>2658</v>
+        <v>2660</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1055,7 +1059,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jh4332@naver.com</t>
+          <t>ekf1121_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q7" t="n">
         <v>56</v>
       </c>
       <c r="R7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1148,12 +1152,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>유제이 PT&amp;필라테스 노형점</t>
+          <t>케이휘트니스 삼화점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ohssang988@naver.com</t>
+          <t>k_fitness_samhwa@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1161,17 +1165,17 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+          <t>제주 제주시 청풍남8길 73 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uj_pt0125</t>
+          <t>https://kfitness.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4n9ww</t>
+          <t>https://talk.naver.com/ct/wmnf2b5</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>975</v>
       </c>
       <c r="Q8" t="n">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="R8" t="n">
-        <v>316</v>
+        <v>1279</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1722027239</t>
+          <t>1955946764</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722027239</t>
+          <t>https://m.place.naver.com/place/1955946764</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>트리플짐</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jejutriplegym@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1309-9085</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 동문로16길 5 2층</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jejutriplegym</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>1538</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>541</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>2079</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2028777149</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028777149</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1331,34 +1339,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>휴메이크휘트니스 이도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>humake_ido@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1341-0145</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 과천로 31 4층</t>
+          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jejuatlas/</t>
+          <t>https://blog.naver.com/humake_ido</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfqcj</t>
+          <t>https://talk.naver.com/ct/whys2qr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>129</v>
+        <v>617</v>
       </c>
       <c r="Q10" t="n">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="R10" t="n">
-        <v>317</v>
+        <v>765</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37264400</t>
+          <t>965909506</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37264400</t>
+          <t>https://m.place.naver.com/place/965909506</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>트레이닝 스타</t>
+          <t>아틀라스&amp;바른자세 운동센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trainingstar@naver.com</t>
+          <t>atlascs@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1325-9817</t>
+          <t>0507-1341-0145</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 노형로 353 3층</t>
+          <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trainingstar</t>
+          <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dvi3</t>
+          <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="R11" t="n">
-        <v>71</v>
+        <v>317</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1875737855</t>
+          <t>37264400</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875737855</t>
+          <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>사람휘트니스 이도7호점</t>
+          <t>정글짐 구남점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>saram_ido@naver.com</t>
+          <t>junglegyminherfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1404-1264</t>
+          <t>0507-1380-2950</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 424</t>
+          <t>제주 제주시 구남동8길 58 올레마트 2층 정글짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/saram_ido</t>
+          <t>https://blog.naver.com/junglegyminherfit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yc0j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>273</v>
+        <v>126</v>
       </c>
       <c r="Q2" t="n">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="R2" t="n">
-        <v>734</v>
+        <v>211</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1089331988</t>
+          <t>1471742099</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089331988</t>
+          <t>https://m.place.naver.com/place/1471742099</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>맥시멈 스포츠&amp;웰니스</t>
+          <t>마인드휘트니스 중앙점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>maximum_jeju@naver.com</t>
+          <t>mindfitness23@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1313-9534</t>
+          <t>0507-1468-2371</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
+          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/maximum_jeju</t>
+          <t>https://blog.naver.com/mindfitness23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wha4q04</t>
+          <t>https://talk.naver.com/ct/wo03pkw</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>321</v>
+        <v>1538</v>
       </c>
       <c r="Q3" t="n">
-        <v>1374</v>
+        <v>541</v>
       </c>
       <c r="R3" t="n">
-        <v>1695</v>
+        <v>2079</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1899196588</t>
+          <t>1840405943</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899196588</t>
+          <t>https://m.place.naver.com/place/1840405943</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>유휘트니스 센트럴점</t>
+          <t>맥시멈 스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ecodnc_jeju@naver.com</t>
+          <t>maximum_jeju@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1338-7221</t>
+          <t>0507-1313-9534</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 신대로 104 2층 유휘트니��</t>
+          <t>제주 서귀포시 대정읍 중산간서로 2324-10 맥시멈스포츠&amp;웰니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ecodnc_jeju</t>
+          <t>https://blog.naver.com/maximum_jeju</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44oiy</t>
+          <t>https://talk.naver.com/ct/wha4q04</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1825</v>
+        <v>321</v>
       </c>
       <c r="Q4" t="n">
-        <v>1074</v>
+        <v>1375</v>
       </c>
       <c r="R4" t="n">
-        <v>2899</v>
+        <v>1696</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1478286020</t>
+          <t>1899196588</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478286020</t>
+          <t>https://m.place.naver.com/place/1899196588</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리빌드짐 제주점</t>
+          <t>유휘트니스 센트럴점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>redgym-jeju@naver.com</t>
+          <t>ecodnc_jeju@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1497-3704</t>
+          <t>0507-1338-7221</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
+          <t>제주 제주시 신대로 104 2층 유휘트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rebuildgym_jeju/</t>
+          <t>https://blog.naver.com/ecodnc_jeju</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4syol</t>
+          <t>https://talk.naver.com/ct/w44oiy</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1764</v>
+        <v>1826</v>
       </c>
       <c r="Q5" t="n">
-        <v>92</v>
+        <v>1074</v>
       </c>
       <c r="R5" t="n">
-        <v>1856</v>
+        <v>2900</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1406686676</t>
+          <t>1478286020</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406686676</t>
+          <t>https://m.place.naver.com/place/1478286020</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마인드휘트니스 제주공항점</t>
+          <t>리빌드짐 제주점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mindfitness13@naver.com</t>
+          <t>redgym-jeju@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1348-0798</t>
+          <t>0507-1497-3704</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
+          <t>제주 제주시 중앙로8길 8 리빌드짐 제주점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness13</t>
+          <t>https://www.instagram.com/rebuildgym_jeju/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptgx</t>
+          <t>https://talk.naver.com/ct/wn4syol</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2153</v>
+        <v>1764</v>
       </c>
       <c r="Q6" t="n">
-        <v>507</v>
+        <v>92</v>
       </c>
       <c r="R6" t="n">
-        <v>2660</v>
+        <v>1856</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1102972683</t>
+          <t>1406686676</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102972683</t>
+          <t>https://m.place.naver.com/place/1406686676</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F45 제주</t>
+          <t>마인드휘트니스 제주공항점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ekf1121_@naver.com</t>
+          <t>mindfitness13@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1388-4889</t>
+          <t>0507-1348-0798</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 377 2층</t>
+          <t>제주 제주시 도령로 167 에이동 2층, 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_jeju_</t>
+          <t>https://blog.naver.com/mindfitness13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xp35</t>
+          <t>https://talk.naver.com/ct/w4ptgx</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>74</v>
+        <v>2153</v>
       </c>
       <c r="Q7" t="n">
-        <v>56</v>
+        <v>507</v>
       </c>
       <c r="R7" t="n">
-        <v>130</v>
+        <v>2660</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1238964473</t>
+          <t>1102972683</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1238964473</t>
+          <t>https://m.place.naver.com/place/1102972683</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,30 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>케이휘트니스 삼화점</t>
+          <t>F45 제주</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>k_fitness_samhwa@naver.com</t>
+          <t>ekf1121_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1388-4889</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 청풍남8길 73 5층</t>
+          <t>제주 제주시 중앙로 377 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://kfitness.clickn.co.kr/</t>
+          <t>https://www.instagram.com/f45_jeju_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmnf2b5</t>
+          <t>https://talk.naver.com/ct/w5xp35</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>975</v>
+        <v>74</v>
       </c>
       <c r="Q8" t="n">
-        <v>304</v>
+        <v>56</v>
       </c>
       <c r="R8" t="n">
-        <v>1279</v>
+        <v>130</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1955946764</t>
+          <t>1238964473</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955946764</t>
+          <t>https://m.place.naver.com/place/1238964473</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1246,34 +1246,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마인드휘트니스 중앙점</t>
+          <t>케이휘트니스 삼화점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mindfitness23@naver.com</t>
+          <t>k_fitness_samhwa@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1468-2371</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 중앙로 53 JJ아트뷰타워 3, 4층</t>
+          <t>제주 제주시 청풍남8길 73 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness23</t>
+          <t>https://kfitness.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wo03pkw</t>
+          <t>https://talk.naver.com/ct/wmnf2b5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1538</v>
+        <v>975</v>
       </c>
       <c r="Q9" t="n">
-        <v>541</v>
+        <v>304</v>
       </c>
       <c r="R9" t="n">
-        <v>2079</v>
+        <v>1279</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1840405943</t>
+          <t>1955946764</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840405943</t>
+          <t>https://m.place.naver.com/place/1955946764</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1426,105 +1422,199 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아틀라스&amp;바른자세 운동센터</t>
+          <t>유제이 PT&amp;필라테스 노형점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>atlascs@naver.com</t>
+          <t>ohssang988@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1341-0145</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uj_pt0125</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wn4n9ww</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>140</v>
+      </c>
+      <c r="R11" t="n">
+        <v>315</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1722027239</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1722027239</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>아틀라스&amp;바른자세 운동센터</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>atlascs@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1341-0145</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>제주 제주시 과천로 31 4층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://www.instagram.com/jejuatlas/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/wcfqcj</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>129</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>188</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>317</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>37264400</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/37264400</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/제주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/제주_헬스장.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -820,10 +820,10 @@
         <v>321</v>
       </c>
       <c r="Q4" t="n">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="R4" t="n">
-        <v>1696</v>
+        <v>1701</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 이도점</t>
+          <t>원핏 시청점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humake_ido@naver.com</t>
+          <t>onegdrgolfacademy@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1353,12 +1353,12 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
+          <t>제주 제주시 광양10길 10 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humake_ido</t>
+          <t>https://www.instagram.com/onefit_cityhall?igsh=dGM0ejgzNnN6czI3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whys2qr</t>
+          <t>https://talk.naver.com/ct/w5wrop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>617</v>
+        <v>406</v>
       </c>
       <c r="Q10" t="n">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="R10" t="n">
-        <v>765</v>
+        <v>452</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>965909506</t>
+          <t>1517075976</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/965909506</t>
+          <t>https://m.place.naver.com/place/1517075976</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유제이 PT&amp;필라테스 노형점</t>
+          <t>휴메이크휘트니스 이도점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ohssang988@naver.com</t>
+          <t>humake_ido@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1447,12 +1447,12 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 남녕로 25 리안스테이노형 3층 302호</t>
+          <t>제주 제주시 연삼로 411 네오캠퍼스 2층 휴메이크휘트니스 제주이도점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uj_pt0125</t>
+          <t>https://blog.naver.com/humake_ido</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wn4n9ww</t>
+          <t>https://talk.naver.com/ct/whys2qr</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>175</v>
+        <v>617</v>
       </c>
       <c r="Q11" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="R11" t="n">
-        <v>315</v>
+        <v>765</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1722027239</t>
+          <t>965909506</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722027239</t>
+          <t>https://m.place.naver.com/place/965909506</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
